--- a/results/supplementary/Supplementary_Table_S6_colocalisation_and_provenance.xlsx
+++ b/results/supplementary/Supplementary_Table_S6_colocalisation_and_provenance.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Conditional coloc'!$A$1:$S$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Conditional signals'!$A$1:$N$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Conditional SNPs'!$A$1:$H$1342</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Data manifest'!$A$1:$E$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Data manifest'!$A$1:$E$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -47583,7 +47583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -47923,37 +47923,37 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gnomad/gnomad.v4.1.constraint_metrics.tsv</t>
+          <t>data/raw/go/go-basic.obo</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>https://storage.googleapis.com/gcp-public-data--gnomad/release/4.1/constraint/gnomad.v4.1.constraint_metrics.tsv</t>
+          <t>https://current.geneontology.org/ontology/go-basic.obo</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:12:35Z</t>
+          <t>2026-10-30T16:15:47Z</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>95546041</v>
+        <v>32227785</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14df4b2acb581fcbbb2a82a3a555fd35</t>
+          <t>26de643e50af9a1588f9a31062348cc4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>data/raw/go/go-basic.obo</t>
+          <t>data/raw/go/goa_human.gaf.gz</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://current.geneontology.org/ontology/go-basic.obo</t>
+          <t>https://current.geneontology.org/annotations/goa_human.gaf.gz</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -47962,248 +47962,248 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>32227785</v>
+        <v>15041996</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26de643e50af9a1588f9a31062348cc4</t>
+          <t>3d16e91814f541afc3cdb03153ae0f55</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>data/raw/go/goa_human.gaf.gz</t>
+          <t>data/raw/gwas/GCST007565_README.txt</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://current.geneontology.org/annotations/goa_human.gaf.gz</t>
+          <t>https://ftp.ebi.ac.uk/pub/databases/gwas/summary_statistics/GCST007001-GCST008000/GCST007565/morning_person_README.txt</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:15:47Z</t>
+          <t>2026-10-30T16:22:13Z</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>15041996</v>
+        <v>2357</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3d16e91814f541afc3cdb03153ae0f55</t>
+          <t>e4ffe55b6f87539e112d21cde0264442</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/GCST007565_README.txt</t>
+          <t>data/raw/gwas/GCST007565_morning_person_UKB.txt.gz</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>https://ftp.ebi.ac.uk/pub/databases/gwas/summary_statistics/GCST007001-GCST008000/GCST007565/morning_person_README.txt</t>
+          <t>https://ftp.ebi.ac.uk/pub/databases/gwas/summary_statistics/GCST007001-GCST008000/GCST007565/morning_person_BOLT.output_HRC.only_plus.metrics_maf0.001_hwep1em12_info0.3_logORs.txt.gz</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:22:13Z</t>
+          <t>2026-10-30T16:22:12Z</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2357</v>
+        <v>354578112</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>e4ffe55b6f87539e112d21cde0264442</t>
+          <t>7bb800386e3207e36399af73673eb099</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/GCST007565_morning_person_UKB.txt.gz</t>
+          <t>data/raw/gwas/GCST007576_README.txt</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>https://ftp.ebi.ac.uk/pub/databases/gwas/summary_statistics/GCST007001-GCST008000/GCST007565/morning_person_BOLT.output_HRC.only_plus.metrics_maf0.001_hwep1em12_info0.3_logORs.txt.gz</t>
+          <t>https://ftp.ebi.ac.uk/pub/databases/gwas/summary_statistics/GCST007001-GCST008000/GCST007576/chronotype_README.txt</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:22:12Z</t>
+          <t>2026-10-30T16:15:18Z</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>354578112</v>
+        <v>1608</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7bb800386e3207e36399af73673eb099</t>
+          <t>6e804def5e956eb4dbf9e80922d3e038</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/GCST007576_README.txt</t>
+          <t>data/raw/gwas/GCST007576_chronotype_UKB.txt.gz</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>https://ftp.ebi.ac.uk/pub/databases/gwas/summary_statistics/GCST007001-GCST008000/GCST007576/chronotype_README.txt</t>
+          <t>https://ftp.ebi.ac.uk/pub/databases/gwas/summary_statistics/GCST007001-GCST008000/GCST007576/chronotype_raw_BOLT.output_HRC.only_plus.metrics_maf0.001_hwep1em12_info0.3.txt.gz</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:15:18Z</t>
+          <t>2026-10-30T16:15:11Z</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1608</v>
+        <v>354552319</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6e804def5e956eb4dbf9e80922d3e038</t>
+          <t>2f65481f222ffe5ca652d09ca8a5e2ad</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/GCST007576_chronotype_UKB.txt.gz</t>
+          <t>data/raw/gwas/jones2019_esm/jones2019_DescriptionOfAdditionalSupplementaryFiles.pdf</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>https://ftp.ebi.ac.uk/pub/databases/gwas/summary_statistics/GCST007001-GCST008000/GCST007576/chronotype_raw_BOLT.output_HRC.only_plus.metrics_maf0.001_hwep1em12_info0.3.txt.gz</t>
+          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM3_ESM.pdf</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:15:11Z</t>
+          <t>2026-10-30T16:12:15Z</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>354552319</v>
+        <v>300882</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2f65481f222ffe5ca652d09ca8a5e2ad</t>
+          <t>c25c65d8627eedfea4f79bdf8d8a272f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/jones2019_esm/jones2019_DescriptionOfAdditionalSupplementaryFiles.pdf</t>
+          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData1.xlsx</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM3_ESM.pdf</t>
+          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM4_ESM.xlsx</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:12:15Z</t>
+          <t>2026-10-30T16:12:08Z</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>300882</v>
+        <v>132312</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>c25c65d8627eedfea4f79bdf8d8a272f</t>
+          <t>ab76158a14777ac9efd7ea0a9577edb1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData1.xlsx</t>
+          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData10.xlsx</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM4_ESM.xlsx</t>
+          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM13_ESM.xlsx</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:12:08Z</t>
+          <t>2026-10-30T16:12:11Z</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>132312</v>
+        <v>1790254</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>ab76158a14777ac9efd7ea0a9577edb1</t>
+          <t>04a614363d9a756ff825acd3a78b535b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData10.xlsx</t>
+          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData11.xlsx</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM13_ESM.xlsx</t>
+          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM14_ESM.xlsx</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:12:11Z</t>
+          <t>2026-10-30T16:12:12Z</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1790254</v>
+        <v>39105</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>04a614363d9a756ff825acd3a78b535b</t>
+          <t>05b116d0aba017d0ca5a6eb00fe62c38</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData11.xlsx</t>
+          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData12.xlsx</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM14_ESM.xlsx</t>
+          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM15_ESM.xlsx</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:12:12Z</t>
+          <t>2026-10-30T16:12:13Z</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>39105</v>
+        <v>13409</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>05b116d0aba017d0ca5a6eb00fe62c38</t>
+          <t>7e58643301a12ac05a759a875f6bfe39</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData12.xlsx</t>
+          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData13.xlsx</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM15_ESM.xlsx</t>
+          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM16_ESM.xlsx</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -48212,48 +48212,48 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>13409</v>
+        <v>13865</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7e58643301a12ac05a759a875f6bfe39</t>
+          <t>28f438dd10ab97bf2571f682639f1794</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData13.xlsx</t>
+          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData14.txt</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM16_ESM.xlsx</t>
+          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM17_ESM.txt</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:12:13Z</t>
+          <t>2026-10-30T16:12:14Z</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>13865</v>
+        <v>5451</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28f438dd10ab97bf2571f682639f1794</t>
+          <t>03888ac0cdba231ab4fa2e42d6051635</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData14.txt</t>
+          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData15.xlsx</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM17_ESM.txt</t>
+          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM18_ESM.xlsx</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -48262,48 +48262,48 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>5451</v>
+        <v>22132</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>03888ac0cdba231ab4fa2e42d6051635</t>
+          <t>b6c3d0e852331335bd01886259d3543f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData15.xlsx</t>
+          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData2.xlsx</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM18_ESM.xlsx</t>
+          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM5_ESM.xlsx</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:12:14Z</t>
+          <t>2026-10-30T16:12:08Z</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>22132</v>
+        <v>74191</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>b6c3d0e852331335bd01886259d3543f</t>
+          <t>2ff2a26a6aa5c03f02b879c491ffb93d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData2.xlsx</t>
+          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData3.xlsx</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM5_ESM.xlsx</t>
+          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM6_ESM.xlsx</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -48312,48 +48312,48 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>74191</v>
+        <v>194402</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2ff2a26a6aa5c03f02b879c491ffb93d</t>
+          <t>fb4add71faf19b8d866fcec3bcfcbae9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData3.xlsx</t>
+          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData4.xlsx</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM6_ESM.xlsx</t>
+          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM7_ESM.xlsx</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:12:08Z</t>
+          <t>2026-10-30T16:12:09Z</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>194402</v>
+        <v>792430</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>fb4add71faf19b8d866fcec3bcfcbae9</t>
+          <t>f1842162b4d29a13a634f58aed63ba66</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData4.xlsx</t>
+          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData5.xlsx</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM7_ESM.xlsx</t>
+          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM8_ESM.xlsx</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -48362,48 +48362,48 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>792430</v>
+        <v>60396</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>f1842162b4d29a13a634f58aed63ba66</t>
+          <t>fdbdae222874b56f65fc1d0e509e000a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData5.xlsx</t>
+          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData6.xlsx</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM8_ESM.xlsx</t>
+          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM9_ESM.xlsx</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:12:09Z</t>
+          <t>2026-10-30T16:12:10Z</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>60396</v>
+        <v>383436</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>fdbdae222874b56f65fc1d0e509e000a</t>
+          <t>a03caeb903cefb9c267b7b2949ee7fef</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData6.xlsx</t>
+          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData7.xlsx</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM9_ESM.xlsx</t>
+          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM10_ESM.xlsx</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -48412,23 +48412,23 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>383436</v>
+        <v>1851977</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>a03caeb903cefb9c267b7b2949ee7fef</t>
+          <t>f52611aa1c02e49712986df977addb71</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData7.xlsx</t>
+          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData8.xlsx</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM10_ESM.xlsx</t>
+          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM11_ESM.xlsx</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -48437,98 +48437,98 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1851977</v>
+        <v>39758</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>f52611aa1c02e49712986df977addb71</t>
+          <t>f05bf4867dd737b100b37c39dae70242</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData8.xlsx</t>
+          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData9.xlsx</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM11_ESM.xlsx</t>
+          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM12_ESM.xlsx</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:12:10Z</t>
+          <t>2026-10-30T16:12:11Z</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>39758</v>
+        <v>42460</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>f05bf4867dd737b100b37c39dae70242</t>
+          <t>102d689a26d05cb9238c90084c51cf26</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryData9.xlsx</t>
+          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryInformation.pdf</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM12_ESM.xlsx</t>
+          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM1_ESM.pdf</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:12:11Z</t>
+          <t>2026-10-30T16:12:15Z</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>42460</v>
+        <v>1802130</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>102d689a26d05cb9238c90084c51cf26</t>
+          <t>fa4f81fe3feb45cfa46cf7bf3857acac</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>data/raw/gwas/jones2019_esm/jones2019_SupplementaryInformation.pdf</t>
+          <t>data/raw/hpo/genes_to_disease.txt</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>https://media.springernature.com/original/springer-static/esm/art%3A10.1038%2Fs41467-018-08259-7/MediaObjects/41467_2018_8259_MOESM1_ESM.pdf</t>
+          <t>https://github.com/obophenotype/human-phenotype-ontology/releases/latest/download/genes_to_disease.txt</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:12:15Z</t>
+          <t>2026-10-30T16:12:30Z</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1802130</v>
+        <v>1492039</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>fa4f81fe3feb45cfa46cf7bf3857acac</t>
+          <t>337ee42c2c17f2d89ec5d21ba7515c67</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>data/raw/hpo/genes_to_disease.txt</t>
+          <t>data/raw/hpo/genes_to_phenotype.txt</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/obophenotype/human-phenotype-ontology/releases/latest/download/genes_to_disease.txt</t>
+          <t>https://github.com/obophenotype/human-phenotype-ontology/releases/latest/download/genes_to_phenotype.txt</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -48537,118 +48537,118 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1492039</v>
+        <v>20821704</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>337ee42c2c17f2d89ec5d21ba7515c67</t>
+          <t>6dac74395b2a9192dc0e71594093594f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>data/raw/hpo/genes_to_phenotype.txt</t>
+          <t>data/raw/hpo/hp.obo</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/obophenotype/human-phenotype-ontology/releases/latest/download/genes_to_phenotype.txt</t>
+          <t>https://github.com/obophenotype/human-phenotype-ontology/releases/latest/download/hp.obo</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:12:30Z</t>
+          <t>2026-10-30T16:12:28Z</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>20821704</v>
+        <v>10863613</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>6dac74395b2a9192dc0e71594093594f</t>
+          <t>97620d1eae29ff3665ee644a7315b0f1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>data/raw/hpo/hp.obo</t>
+          <t>data/raw/hpo/phenotype.hpoa</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/obophenotype/human-phenotype-ontology/releases/latest/download/hp.obo</t>
+          <t>https://github.com/obophenotype/human-phenotype-ontology/releases/latest/download/phenotype.hpoa</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:12:28Z</t>
+          <t>2026-10-30T16:12:29Z</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>10863613</v>
+        <v>35816037</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>97620d1eae29ff3665ee644a7315b0f1</t>
+          <t>b4125a21c9ba916d10ce7551e55ead53</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>data/raw/hpo/phenotype.hpoa</t>
+          <t>data/raw/ldref/g1000_eur.zip</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/obophenotype/human-phenotype-ontology/releases/latest/download/phenotype.hpoa</t>
+          <t>https://vu.data.surfsara.nl/index.php/s/VZNByNwpD8qqINe/download</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:12:29Z</t>
+          <t>2026-10-30T16:09:09Z</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>35816037</v>
+        <v>511626945</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>b4125a21c9ba916d10ce7551e55ead53</t>
+          <t>1919cb5c79bbe7871aed71ae4abe6217</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>data/raw/ldref/g1000_eur.zip</t>
+          <t>data/raw/opentargets/credible_sets.json</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>https://vu.data.surfsara.nl/index.php/s/VZNByNwpD8qqINe/download</t>
+          <t>https://api.platform.opentargets.org/api/v4/graphql (Open Targets Platform 26.09; queries in scripts/08_fetch_opentargets.py and 08b_fetch_opentargets_qtl.py)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:09:09Z</t>
+          <t>2026-10-30T17:00:23Z</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>511626945</v>
+        <v>48285792</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1919cb5c79bbe7871aed71ae4abe6217</t>
+          <t>897416946e3c176086201a70f95ca69e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>data/raw/opentargets/credible_sets.json</t>
+          <t>data/raw/opentargets/meta.json</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -48658,270 +48658,295 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T17:00:23Z</t>
+          <t>2026-10-30T16:38:42Z</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>48285792</v>
+        <v>229</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>897416946e3c176086201a70f95ca69e</t>
+          <t>10666c685c00372a4ecec4898bb91627</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>data/raw/opentargets/meta.json</t>
+          <t>data/raw/orphanet/en_product6.xml</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>https://api.platform.opentargets.org/api/v4/graphql (Open Targets Platform 26.09; queries in scripts/08_fetch_opentargets.py and 08b_fetch_opentargets_qtl.py)</t>
+          <t>https://www.orphadata.com/data/xml/en_product6.xml</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:38:42Z</t>
+          <t>2026-10-30T16:13:45Z</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>229</v>
+        <v>22612034</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>10666c685c00372a4ecec4898bb91627</t>
+          <t>83dcbf35a29393f27ba2683f157977f2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>data/raw/orphanet/en_product6.xml</t>
+          <t>data/raw/panelapp/green_genes.tsv</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>https://www.orphadata.com/data/xml/en_product6.xml</t>
+          <t>https://panelapp.genomicsengland.co.uk/api/v1 (Genomics England PanelApp REST API; scripts/01b_fetch_panelapp.py)</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:13:45Z</t>
+          <t>2026-10-30T20:05:26Z</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>22612034</v>
+        <v>3722303</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>83dcbf35a29393f27ba2683f157977f2</t>
+          <t>30d5917cd44afb1a7a3b51fe16ca48ba</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>data/raw/qt/GCST90165291_QT_buildGRCh37.tsv.gz</t>
+          <t>data/raw/panelapp/panels.tsv</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>https://ftp.ebi.ac.uk/pub/databases/gwas/summary_statistics/GCST90165001-GCST90166000/GCST90165291/GCST90165291_buildGRCh37.tsv.gz</t>
+          <t>https://panelapp.genomicsengland.co.uk/api/v1 (Genomics England PanelApp REST API; scripts/01b_fetch_panelapp.py)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T17:05:28Z</t>
+          <t>2026-10-30T19:56:48Z</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>553566004</v>
+        <v>48198</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>67e36ee29baa10ea35b4f92e1a749751</t>
+          <t>3e29cdceeb1c12b8309de50a4e2f0743</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>data/raw/rhythm/GPL6246.annot.gz</t>
+          <t>data/raw/qt/GCST90165291_QT_buildGRCh37.tsv.gz</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>https://ftp.ncbi.nlm.nih.gov/geo/platforms/GPL6nnn/GPL6246/annot/GPL6246.annot.gz</t>
+          <t>https://ftp.ebi.ac.uk/pub/databases/gwas/summary_statistics/GCST90165001-GCST90166000/GCST90165291/GCST90165291_buildGRCh37.tsv.gz</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:48:10Z</t>
+          <t>2026-10-30T17:05:28Z</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>7325203</v>
+        <v>553566004</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>558236e542f0fbd3859a2cea989f7f74</t>
+          <t>67e36ee29baa10ea35b4f92e1a749751</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>data/raw/rhythm/GSE54650_series_matrix.txt.gz</t>
+          <t>data/raw/rhythm/GPL6246.annot.gz</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>https://ftp.ncbi.nlm.nih.gov/geo/series/GSE54nnn/GSE54650/matrix/GSE54650_series_matrix.txt.gz</t>
+          <t>https://ftp.ncbi.nlm.nih.gov/geo/platforms/GPL6nnn/GPL6246/annot/GPL6246.annot.gz</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:48:09Z</t>
+          <t>2026-10-30T16:48:10Z</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>20423134</v>
+        <v>7325203</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>4e0d1ae8a4defdbf7d2bf377dc752dc4</t>
+          <t>558236e542f0fbd3859a2cea989f7f74</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>data/raw/rhythm/HOM_MouseHumanSequence.rpt</t>
+          <t>data/raw/rhythm/GSE54650_series_matrix.txt.gz</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>https://www.informatics.jax.org/downloads/reports/HOM_MouseHumanSequence.rpt</t>
+          <t>https://ftp.ncbi.nlm.nih.gov/geo/series/GSE54nnn/GSE54650/matrix/GSE54650_series_matrix.txt.gz</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:48:11Z</t>
+          <t>2026-10-30T16:48:09Z</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>15112913</v>
+        <v>20423134</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1870775745ab5c05c822f925134ced98</t>
+          <t>4e0d1ae8a4defdbf7d2bf377dc752dc4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>data/raw/rhythm/wucher2023_S1_daynight.tab.gz</t>
+          <t>data/raw/rhythm/HOM_MouseHumanSequence.rpt</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>https://ndownloader.figshare.com/files/38858706</t>
+          <t>https://www.informatics.jax.org/downloads/reports/HOM_MouseHumanSequence.rpt</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:46:39Z</t>
+          <t>2026-10-30T16:48:11Z</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>45837571</v>
+        <v>15112913</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>a236790a81f9a6389ce30d1711bfcb84</t>
+          <t>1870775745ab5c05c822f925134ced98</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>data/raw/tools/magma_v1.10_static.zip</t>
+          <t>data/raw/rhythm/wucher2023_S1_daynight.tab.gz</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>https://vu.data.surfsara.nl/index.php/s/lxDgt2dNdNr6DYt/download</t>
+          <t>https://ndownloader.figshare.com/files/38858706</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:08:53Z</t>
+          <t>2026-10-30T16:46:39Z</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>3278944</v>
+        <v>45837571</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>e01c9ec24c7dd96d2f95477080bf7ad4</t>
+          <t>a236790a81f9a6389ce30d1711bfcb84</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>data/raw/tools/plink2_linux_x86_64_20250129.zip</t>
+          <t>data/raw/tools/magma_v1.10_static.zip</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>https://s3.amazonaws.com/plink2-assets/alpha6/plink2_linux_x86_64_20250129.zip</t>
+          <t>https://vu.data.surfsara.nl/index.php/s/lxDgt2dNdNr6DYt/download</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:08:50Z</t>
+          <t>2026-10-30T16:08:53Z</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>10368992</v>
+        <v>3278944</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>aa23bd021c479e11588441dc5042aaef</t>
+          <t>e01c9ec24c7dd96d2f95477080bf7ad4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>data/raw/tools/plink2_linux_x86_64_20250129.zip</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/plink2-assets/alpha6/plink2_linux_x86_64_20250129.zip</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T16:08:50Z</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>10368992</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>aa23bd021c479e11588441dc5042aaef</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
           <t>data/raw/tools/plink_linux_x86_64_20231211.zip</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>https://s3.amazonaws.com/plink1-assets/plink_linux_x86_64_20231211.zip</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>2026-10-30T16:08:49Z</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D54" s="2" t="n">
         <v>8953953</v>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>5d1e6c2f1b7c3bfd2af5f80e51714c8b</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E53"/>
+  <autoFilter ref="A1:E54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>